--- a/backend/data/CS_courses.xlsx
+++ b/backend/data/CS_courses.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="87">
   <si>
     <t>课程名称</t>
   </si>
@@ -122,6 +122,183 @@
       </rPr>
       <t>与大数据实战（挑战性课程）</t>
     </r>
+  </si>
+  <si>
+    <t>计算机导论</t>
+  </si>
+  <si>
+    <t>专业方向选修课</t>
+  </si>
+  <si>
+    <t>固件安全</t>
+  </si>
+  <si>
+    <t>计算机图形学</t>
+  </si>
+  <si>
+    <t>数字图像处理</t>
+  </si>
+  <si>
+    <t>数据结构与算法竞赛实验</t>
+  </si>
+  <si>
+    <t>UNIX操作系统</t>
+  </si>
+  <si>
+    <t>系统软件设计与实现I——操作系统</t>
+  </si>
+  <si>
+    <t>组合数学</t>
+  </si>
+  <si>
+    <t>计算数学基础</t>
+  </si>
+  <si>
+    <t>数据挖掘与大数据分析</t>
+  </si>
+  <si>
+    <t>软件工程</t>
+  </si>
+  <si>
+    <t>算法与计算理论</t>
+  </si>
+  <si>
+    <t>系统硬件综合实验</t>
+  </si>
+  <si>
+    <t>最优化算法</t>
+  </si>
+  <si>
+    <t>系统软件设计与实现II——编译系统</t>
+  </si>
+  <si>
+    <t>分布式并行计算</t>
+  </si>
+  <si>
+    <t>计算机视觉与模式识别</t>
+  </si>
+  <si>
+    <t>嵌入式系统及应用</t>
+  </si>
+  <si>
+    <t>智能计算系统</t>
+  </si>
+  <si>
+    <t>数据可视化</t>
+  </si>
+  <si>
+    <t>智能决策与强化学习</t>
+  </si>
+  <si>
+    <t>系统软件设计与实现III——数据库系统</t>
+  </si>
+  <si>
+    <t>自然语言处理</t>
+  </si>
+  <si>
+    <t>三维图形程序设计</t>
+  </si>
+  <si>
+    <t>汇编语言与微机接口技术</t>
+  </si>
+  <si>
+    <t>计算机网络编程</t>
+  </si>
+  <si>
+    <t>游戏设计</t>
+  </si>
+  <si>
+    <t>插件式画板设计与实现</t>
+  </si>
+  <si>
+    <t>软件工程综合实验</t>
+  </si>
+  <si>
+    <t>计算机网络安全实验</t>
+  </si>
+  <si>
+    <t>计算机系统安全实验</t>
+  </si>
+  <si>
+    <t>AI处理器架构与设计</t>
+  </si>
+  <si>
+    <t>软件开发系统级技术基础</t>
+  </si>
+  <si>
+    <t>汇编语言与微机接口技术综合实验</t>
+  </si>
+  <si>
+    <t>云计算基础及实践（企业级认证课程）</t>
+  </si>
+  <si>
+    <t>自底向上的计算机病毒原理与实践</t>
+  </si>
+  <si>
+    <t>Linux系统编程</t>
+  </si>
+  <si>
+    <t>软件工程安全实验（华为共建实践课程）</t>
+  </si>
+  <si>
+    <t>高级计算机图形学</t>
+  </si>
+  <si>
+    <t>音视频处理技术</t>
+  </si>
+  <si>
+    <t>人机交互</t>
+  </si>
+  <si>
+    <t>摄影原理与技术</t>
+  </si>
+  <si>
+    <t>计算机视觉（挑战性课程）</t>
+  </si>
+  <si>
+    <t>计算机组成与系统结构I-电路与数字逻辑</t>
+  </si>
+  <si>
+    <t>计算机组成与系统结构II-组成与结构</t>
+  </si>
+  <si>
+    <t>计算机网络综合实验</t>
+  </si>
+  <si>
+    <t>系统软件原理与设计II-编译系统</t>
+  </si>
+  <si>
+    <t>汇编语言程序设计</t>
+  </si>
+  <si>
+    <t>信息检索</t>
+  </si>
+  <si>
+    <t>无线安全</t>
+  </si>
+  <si>
+    <t>大数据安全</t>
+  </si>
+  <si>
+    <t>基于操作系统编程技术</t>
+  </si>
+  <si>
+    <t>程序设计语言与编译（挑战性课程）</t>
+  </si>
+  <si>
+    <t>计算机网络</t>
+  </si>
+  <si>
+    <t>社交媒体分析</t>
+  </si>
+  <si>
+    <t>大数据应用技术专题</t>
+  </si>
+  <si>
+    <t>知识表示与推理</t>
+  </si>
+  <si>
+    <t>机器学习前沿</t>
   </si>
 </sst>
 </file>
@@ -146,6 +323,13 @@
       <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -292,13 +476,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
@@ -619,16 +796,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -637,119 +811,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -763,6 +940,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1303,7 +1483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="12.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="42.9090909090909" customWidth="1"/>
@@ -1562,7 +1742,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="13" spans="1:4">
+    <row r="17" ht="13" spans="1:5">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
@@ -1576,7 +1756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" ht="13" spans="1:4">
+    <row r="18" ht="13" spans="1:5">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -1590,7 +1770,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="13" spans="1:4">
+    <row r="19" ht="13" spans="1:5">
       <c r="A19" s="4" t="s">
         <v>27</v>
       </c>
@@ -1603,6 +1783,876 @@
       <c r="D19">
         <v>3</v>
       </c>
+    </row>
+    <row r="20" ht="14" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" ht="14" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2</v>
+      </c>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" ht="14" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3</v>
+      </c>
+      <c r="E22" s="6"/>
+    </row>
+    <row r="23" ht="14" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="6">
+        <v>3</v>
+      </c>
+      <c r="D23" s="6">
+        <v>4</v>
+      </c>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" ht="14" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>4</v>
+      </c>
+      <c r="E24" s="6"/>
+    </row>
+    <row r="25" ht="14" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3</v>
+      </c>
+      <c r="D25" s="6">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6"/>
+    </row>
+    <row r="26" ht="14" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
+      </c>
+      <c r="D26" s="6">
+        <v>4</v>
+      </c>
+      <c r="E26" s="6"/>
+    </row>
+    <row r="27" ht="14" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>5</v>
+      </c>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" ht="14" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3</v>
+      </c>
+      <c r="D28" s="6">
+        <v>5</v>
+      </c>
+      <c r="E28" s="6"/>
+    </row>
+    <row r="29" ht="14" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="6">
+        <v>3</v>
+      </c>
+      <c r="D29" s="6">
+        <v>5</v>
+      </c>
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" ht="14" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="6">
+        <v>3</v>
+      </c>
+      <c r="D30" s="6">
+        <v>5</v>
+      </c>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" ht="14" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="6">
+        <v>2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>5</v>
+      </c>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" ht="14" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="6">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6">
+        <v>5</v>
+      </c>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" ht="14" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="6">
+        <v>3</v>
+      </c>
+      <c r="D33" s="6">
+        <v>5</v>
+      </c>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" ht="14" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="6">
+        <v>2</v>
+      </c>
+      <c r="D34" s="6">
+        <v>5</v>
+      </c>
+      <c r="E34" s="6"/>
+    </row>
+    <row r="35" ht="14" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>6</v>
+      </c>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" ht="14" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2</v>
+      </c>
+      <c r="D36" s="6">
+        <v>6</v>
+      </c>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" ht="14" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="6">
+        <v>3</v>
+      </c>
+      <c r="D37" s="6">
+        <v>6</v>
+      </c>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" ht="14" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>6</v>
+      </c>
+      <c r="E38" s="6"/>
+    </row>
+    <row r="39" ht="14" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="6">
+        <v>3</v>
+      </c>
+      <c r="D39" s="6">
+        <v>6</v>
+      </c>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" ht="14" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="6">
+        <v>3</v>
+      </c>
+      <c r="D40" s="6">
+        <v>6</v>
+      </c>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" ht="14" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="6">
+        <v>2</v>
+      </c>
+      <c r="D41" s="6">
+        <v>6</v>
+      </c>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" ht="14" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="6">
+        <v>3</v>
+      </c>
+      <c r="D42" s="6">
+        <v>6</v>
+      </c>
+      <c r="E42" s="6"/>
+    </row>
+    <row r="43" ht="14" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="6">
+        <v>3</v>
+      </c>
+      <c r="D43" s="6">
+        <v>4</v>
+      </c>
+      <c r="E43" s="6"/>
+    </row>
+    <row r="44" ht="14" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="6">
+        <v>3</v>
+      </c>
+      <c r="D44" s="6">
+        <v>5</v>
+      </c>
+      <c r="E44" s="6"/>
+    </row>
+    <row r="45" ht="14" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" s="6">
+        <v>3</v>
+      </c>
+      <c r="D45" s="6">
+        <v>5</v>
+      </c>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" ht="14" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="6">
+        <v>3</v>
+      </c>
+      <c r="D46" s="6">
+        <v>5</v>
+      </c>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" ht="14" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>5</v>
+      </c>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" ht="14" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
+      <c r="D48" s="6">
+        <v>5</v>
+      </c>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" ht="14" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="6">
+        <v>1</v>
+      </c>
+      <c r="D49" s="6">
+        <v>5</v>
+      </c>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" ht="14" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" s="6">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6">
+        <v>6</v>
+      </c>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" ht="14" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="6">
+        <v>2</v>
+      </c>
+      <c r="D51" s="6">
+        <v>6</v>
+      </c>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" ht="14" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="6">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6">
+        <v>6</v>
+      </c>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" ht="14" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <v>6</v>
+      </c>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" ht="14" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>6</v>
+      </c>
+      <c r="E54" s="6"/>
+    </row>
+    <row r="55" ht="14" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1</v>
+      </c>
+      <c r="D55" s="6">
+        <v>6</v>
+      </c>
+      <c r="E55" s="6"/>
+    </row>
+    <row r="56" ht="14" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="6">
+        <v>3</v>
+      </c>
+      <c r="D56" s="6">
+        <v>6</v>
+      </c>
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" ht="14" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1</v>
+      </c>
+      <c r="D57" s="6">
+        <v>6</v>
+      </c>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="58" ht="14" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" s="6">
+        <v>3</v>
+      </c>
+      <c r="D58" s="6">
+        <v>5</v>
+      </c>
+      <c r="E58" s="6"/>
+    </row>
+    <row r="59" ht="14" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D59" s="6">
+        <v>6</v>
+      </c>
+      <c r="E59" s="6"/>
+    </row>
+    <row r="60" ht="14" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D60" s="6">
+        <v>7</v>
+      </c>
+      <c r="E60" s="6"/>
+    </row>
+    <row r="61" ht="14" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="6">
+        <v>2</v>
+      </c>
+      <c r="D61" s="6">
+        <v>7</v>
+      </c>
+      <c r="E61" s="6"/>
+    </row>
+    <row r="62" ht="14" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="6">
+        <v>3</v>
+      </c>
+      <c r="D62" s="6">
+        <v>6</v>
+      </c>
+      <c r="E62" s="6"/>
+    </row>
+    <row r="63" ht="14" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="D63" s="6">
+        <v>2</v>
+      </c>
+      <c r="E63" s="6"/>
+    </row>
+    <row r="64" ht="14" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="6">
+        <v>4</v>
+      </c>
+      <c r="D64" s="6">
+        <v>3</v>
+      </c>
+      <c r="E64" s="6"/>
+    </row>
+    <row r="65" ht="14" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1</v>
+      </c>
+      <c r="D65" s="6">
+        <v>4</v>
+      </c>
+      <c r="E65" s="6"/>
+    </row>
+    <row r="66" ht="14" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D66" s="6">
+        <v>5</v>
+      </c>
+      <c r="E66" s="6"/>
+    </row>
+    <row r="67" ht="14" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="6">
+        <v>2</v>
+      </c>
+      <c r="D67" s="6">
+        <v>5</v>
+      </c>
+      <c r="E67" s="6"/>
+    </row>
+    <row r="68" ht="14" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="6">
+        <v>2</v>
+      </c>
+      <c r="D68" s="6">
+        <v>5</v>
+      </c>
+      <c r="E68" s="6"/>
+    </row>
+    <row r="69" ht="14" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="6">
+        <v>2</v>
+      </c>
+      <c r="D69" s="6">
+        <v>5</v>
+      </c>
+      <c r="E69" s="6"/>
+    </row>
+    <row r="70" ht="14" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" s="6">
+        <v>2</v>
+      </c>
+      <c r="D70" s="6">
+        <v>6</v>
+      </c>
+      <c r="E70" s="6"/>
+    </row>
+    <row r="71" ht="14" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="6">
+        <v>3</v>
+      </c>
+      <c r="D71" s="6">
+        <v>6</v>
+      </c>
+      <c r="E71" s="6"/>
+    </row>
+    <row r="72" ht="14" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D72" s="6">
+        <v>5</v>
+      </c>
+      <c r="E72" s="6"/>
+    </row>
+    <row r="73" ht="14" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D73" s="6">
+        <v>4</v>
+      </c>
+      <c r="E73" s="6"/>
+    </row>
+    <row r="74" ht="14" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="6">
+        <v>2</v>
+      </c>
+      <c r="D74" s="6">
+        <v>5</v>
+      </c>
+      <c r="E74" s="6"/>
+    </row>
+    <row r="75" ht="14" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="6">
+        <v>2</v>
+      </c>
+      <c r="D75" s="6">
+        <v>5</v>
+      </c>
+      <c r="E75" s="6"/>
+    </row>
+    <row r="76" ht="14" spans="1:5">
+      <c r="A76" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="6">
+        <v>3</v>
+      </c>
+      <c r="D76" s="6">
+        <v>5</v>
+      </c>
+      <c r="E76" s="6"/>
+    </row>
+    <row r="77" ht="14" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="6">
+        <v>3</v>
+      </c>
+      <c r="D77" s="6">
+        <v>5</v>
+      </c>
+      <c r="E77" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
